--- a/backend/data/rule_sets/pre_report_1783391995_a86ed9/source.xlsx
+++ b/backend/data/rule_sets/pre_report_1783391995_a86ed9/source.xlsx
@@ -3328,7 +3328,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"关联交易性质","op":"equals","value":"重大关联交易"},"target":{"field":"关联交易事项.重大关联交易是否已经董事会批准","op":"required"},"raw_spec":"when 关联交易性质选择【重大关联交易】时必填 =&gt; 重大关联交易是否已经董事会批准 必填非空","source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"关联交易事项.关联交易性质","op":"equals","value":"重大关联交易"},"target":{"field":"关联交易事项.重大关联交易是否已经董事会批准","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3364,7 +3364,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
